--- a/exports/colleges/26006_iimc-indian-institute-of-management-kolkata.xlsx
+++ b/exports/colleges/26006_iimc-indian-institute-of-management-kolkata.xlsx
@@ -445,7 +445,7 @@
     <col width="253" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="172" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #7</t>
+          <t>Rank #7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,32 +707,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.5 Lakhs</t>
+          <t>33.5 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation + GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>7 July - 20 Aug 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27 Lakhs</t>
+          <t>27 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation with 50% + CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CAT, GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 May - 08 Jun 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -816,27 +816,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Post Graduate Diploma in Business Analytics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
+          <t>Post Graduate Diploma in Business Analytics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.5 Lakhs</t>
+          <t>27.1 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation + CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>23 Jan - 23 Feb 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -878,27 +878,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Graduate Certificate in Management</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.75 Lakhs</t>
+          <t>18.5 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation with 50%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>7 July - 20 Aug 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,47 +940,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UG Certificate in Management</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Post Graduate Certificate in Family Business Management</t>
+          <t>Ph.D. (Management)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Post Graduate Certificate in Family Business Management</t>
+          <t>Ph.D. (Management)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.56 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Nov - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1002,32 +1002,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27 Lakhs</t>
+          <t>2.75 L - 6.74 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>7 July - 20 Aug 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Management Development Programme</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBA Ex</t>
+          <t>Management Development Programme</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MBA Ex</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.50 Lakhs</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 May - 08 Jun 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PGDBA</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PGDBA</t>
+          <t>General Management Programme for Executives (GMPE)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PGDBA</t>
+          <t>General Management Programme for Executives (GMPE)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25 Lakhs</t>
+          <t>4.5 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 May - 08 Jun 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1188,32 +1188,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Post Graduate Certificate in Family Business Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Post Graduate Certificate in Family Business Management</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25 Lakhs</t>
+          <t>4.56 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 May - 08 Jun 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1250,32 +1250,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caution Deposit</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Caution Deposit</t>
+          <t>Ph.D. (Executive)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Caution Deposit</t>
+          <t>Ph.D. (Executive)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>25 L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Nov - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Master of Business Administration [MBA] (Executive)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Master of Business Administration [MBA] (Executive)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.10 Lakhs</t>
+          <t>33.5 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GMAT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1374,42 +1374,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Executive Programme (General)</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>27 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50% + CAT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, GMAT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1436,25 +1436,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Certification (General)</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Post Graduate Program for Executives for Visionary Leadership In Manufacturing [PGPEX-VLM]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>18.5 Lakhs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1462,12 +1466,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1494,38 +1498,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PG Certificate</t>
+          <t>Graduate Certificate in Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PG Certificate (General)</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>2.75 Lakhs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1540,7 +1548,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1552,42 +1560,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ph.D Executive</t>
+          <t>UG Certificate in Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ph.D Executive (General)</t>
+          <t>Post Graduate Certificate in Family Business Management</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Post Graduate Certificate in Family Business Management</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Post Graduation</t>
+          <t>4.56 Lakhs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1614,22 +1622,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EMBA (General)</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>27 Lakhs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1639,7 +1647,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1676,27 +1684,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Less than 1 year</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Less than 1 year</t>
+          <t>MBA Ex</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Less than 1 year</t>
+          <t>MBA Ex</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>33.50 Lakhs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1711,7 +1719,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1726,7 +1734,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1738,27 +1746,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>PGDBA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>PGDBA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>PGDBA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25 Lakhs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1788,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1808,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Less than 2 years</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Less than 2 years</t>
+          <t>Executive Programme (General)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Less than 2 years</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1850,7 +1858,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1870,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>Certification (General)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1924,29 +1928,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>More than 2 years</t>
+          <t>PG Certificate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>More than 2 years</t>
+          <t>PG Certificate (General)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>More than 2 years</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1986,27 +1986,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Software, IT, Product &amp; Services</t>
+          <t>Ph.D Executive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Software, IT, Product &amp; Services</t>
+          <t>Ph.D Executive (General)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Software, IT, Product &amp; Services</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>Post Graduation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2048,32 +2048,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Engineering, Manufacturing &amp; Energy</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Engineering, Manufacturing &amp; Energy</t>
+          <t>EMBA (General)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Engineering, Manufacturing &amp; Energy</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Consulting &amp; Analytics</t>
+          <t>Software, IT, Product &amp; Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Consulting &amp; Analytics</t>
+          <t>Software, IT, Product &amp; Services</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Consulting &amp; Analytics</t>
+          <t>Software, IT, Product &amp; Services</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2172,22 +2172,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Engineering, Manufacturing &amp; Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Engineering, Manufacturing &amp; Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Engineering, Manufacturing &amp; Energy</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2234,22 +2234,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freshers</t>
+          <t>Consulting &amp; Analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Freshers</t>
+          <t>Consulting &amp; Analytics</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Freshers</t>
+          <t>Consulting &amp; Analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2296,22 +2296,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Advanced Programme in Strategic Management for Corporate Leaders (APSMCL)</t>
+          <t>Freshers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Advanced Programme in Strategic Management for Corporate Leaders (APSMCL)</t>
+          <t>Freshers</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Advanced Programme in Strategic Management for Corporate Leaders (APSMCL)</t>
+          <t>Freshers</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2420,32 +2420,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Executive Programme in General Management (EPGM)</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Executive Programme in General Management (EPGM)</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2482,32 +2482,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Executive Programme</t>
+          <t>Advanced Programme in Strategic Management for Corporate Leaders (APSMCL)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Executive Programme in Leadership and Management (EPLM)</t>
+          <t>Advanced Programme in Strategic Management for Corporate Leaders (APSMCL)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Executive Programme in Leadership and Management (EPLM)</t>
+          <t>Advanced Programme in Strategic Management for Corporate Leaders (APSMCL)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Executive Programme on Business Analytics (EPBA)</t>
+          <t>Executive Programme in General Management (EPGM)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Executive Programme on Business Analytics (EPBA)</t>
+          <t>Executive Programme in General Management (EPGM)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Advanced Programme in Data Sciences (APDS)</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Advanced Programme in Data Sciences (APDS)</t>
+          <t>Executive Programme in Leadership and Management (EPLM)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Advanced Programme in Data Sciences (APDS)</t>
+          <t>Executive Programme in Leadership and Management (EPLM)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2673,12 +2673,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Executive Programme in Human Resource Management (EPHRM)</t>
+          <t>Executive Programme on Business Analytics (EPBA)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Executive Programme in Human Resource Management (EPHRM)</t>
+          <t>Executive Programme on Business Analytics (EPBA)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2730,22 +2730,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EdLEAP: Education Leaders' Programme</t>
+          <t>Advanced Programme in Data Sciences (APDS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EdLEAP: Education Leaders' Programme</t>
+          <t>Advanced Programme in Data Sciences (APDS)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EdLEAP: Education Leaders' Programme</t>
+          <t>Advanced Programme in Data Sciences (APDS)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9 months</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2797,50 +2797,174 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Executive Programme in Human Resource Management (EPHRM)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Executive Programme in Human Resource Management (EPHRM)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Part Time</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>26006</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EdLEAP: Education Leaders' Programme</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EdLEAP: Education Leaders' Programme</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EdLEAP: Education Leaders' Programme</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>26006</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Executive Programme</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Executive Programme in Global Business Management (EPGBM)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Executive Programme in Global Business Management (EPGBM)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>1 year</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1 Year</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -2994,12 +3118,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,45,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>34,23,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3009,7 +3133,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3034,7 +3158,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3073,7 +3197,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CD Rank #7</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
